--- a/financas_onedrive.xlsx
+++ b/financas_onedrive.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,7 +644,6 @@
           <t>Estabelecimento não identificado</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>PicPay</t>
@@ -652,6 +651,282 @@
       </c>
       <c r="F10" t="n">
         <v>118.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no valor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>no valor</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>no valor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>no valor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Matheus Fernandes De Figueiredo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Matheus Fernandes De Figueiredo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>683.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Matheus Fernandes De Figueiredo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Matheus Fernandes De Figueiredo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>683.03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AGF GARANTIDORA DE CONDOMINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C6/PicPay</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BMB DIGITAL NET</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BMB DIGITAL NET</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>74.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BMB DIGITAL NET</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BMB DIGITAL NET</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>74.55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>01/oct</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLARO FLEX</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLARO FLEX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>49.99</v>
       </c>
     </row>
   </sheetData>
